--- a/costing-report-updated-latest.xlsx
+++ b/costing-report-updated-latest.xlsx
@@ -5446,10 +5446,10 @@
         <v>241</v>
       </c>
       <c r="F110" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="G110">
-        <v>3580807</v>
+        <v>5563501</v>
       </c>
       <c r="H110" t="s">
         <v>310</v>

--- a/costing-report-updated-latest.xlsx
+++ b/costing-report-updated-latest.xlsx
@@ -7366,13 +7366,13 @@
         <v>316</v>
       </c>
       <c r="J161" t="s">
-        <v>269</v>
+        <v>285</v>
       </c>
       <c r="K161" t="s">
-        <v>269</v>
+        <v>285</v>
       </c>
       <c r="L161" t="s">
-        <v>269</v>
+        <v>285</v>
       </c>
     </row>
     <row r="162" spans="1:12">

--- a/costing-report-updated-latest.xlsx
+++ b/costing-report-updated-latest.xlsx
@@ -7366,13 +7366,13 @@
         <v>316</v>
       </c>
       <c r="J161" t="s">
-        <v>285</v>
+        <v>269</v>
       </c>
       <c r="K161" t="s">
-        <v>285</v>
+        <v>269</v>
       </c>
       <c r="L161" t="s">
-        <v>285</v>
+        <v>269</v>
       </c>
     </row>
     <row r="162" spans="1:12">
